--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_03_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_03_21_Cau.xlsx
@@ -763,7 +763,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Evidence nào cho biết model đã nhìn thấy case và case đã đổi ra sao?</t>
+          <t>Các biện pháp kiểm soát benchmark đáng tin cậy: (a) Duy trì ID ổn định và lịch sử thay đổi, (b) tách biệt tập public/dev với tập private held-out (để chống overfitting), (c) ghi nhận truy cập và tăng version khi cập nhật, (d) đưa các lỗi production đã xác nhận vào tập living test qua quy trình phê duyệt.</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Filter đánh chất lượng/evidence của candidate, không chỉ acceptance rate.</t>
+          <t>Lý do hợp lệ để loại bỏ một câu hỏi sinh tự động (synthetic candidate): (a) Đáp án kỳ vọng không có căn cứ từ nguồn tài liệu, (b) câu hỏi thiếu dữ kiện để có đáp án duy nhất, (c) trùng lặp ngữ nghĩa với ca kiểm thử đã có, (d) chỉ đổi tên riêng mà không thay đổi bản chất tác vụ.</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -1219,7 +1223,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ đếm call thỏa đủ điều kiện redundant đã nêu.</t>
+          <t>Tỷ lệ redundant tool calls = (2 redundant calls / 8 total tool calls) * 100% = 25%.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_03_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_03_21_Cau.xlsx
@@ -624,10 +624,29 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai mục tiêu sampling cần hai cách diễn giải.
-Phân tích theo nguyên lý thiết kế: Hai mục tiêu sampling cần hai cách diễn giải.</t>
+- 1.0đ: Thiết lập phân bổ tách biệt rõ ràng giữa tập 1.000 ca đại diện và tập 200 ca oversample an toàn.
+- 1.0đ: Xác định phương pháp tính tỷ lệ hiện hành (Prevalence) chỉ dựa trên tập đại diện thực tế.
+- 1.0đ: Thiết lập quy tắc cổng kiểm duyệt an toàn độc lập (Safety Gate) áp dụng chỉ tiêu zero tolerance trên tập oversample.
+- 1.0đ: Lập luận chặt chẽ về việc ngăn chặn méo mó số liệu khi trộn lẫn hai mục tiêu đo lường.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Phân bổ Dữ liệu Phân tầng (Allocation) và Báo cáo Đa mục tiêu (Dual-reporting Strategy):
+1. **Thiết kế Phân bổ Mẫu Độc lập (Dataset Allocation)**:
+- Tuyệt đối **KHÔNG GỘP CHUNG** 1.000 ca production-weighted và 200 ca safety oversample thành một tập 1.200 ca để tính điểm trung bình!
+- Duy trì hai tập dữ liệu độc lập với hai vai trò riêng biệt:
+  + **Tập A: Production-weighted Benchmark (1.000 ca)**: Phản ánh trung thực phân phối thực tế của người dùng ngoài đời thực (đại diện cho tần suất xuất hiện tự nhiên của các chủ đề).
+  + **Tập B: Safety Stress-test Set (200 ca Oversampled)**: Tập trung toàn bộ vào các kịch bản đối kháng nguy hiểm, bẫy bảo mật, và vi phạm chính sách nhạy cảm.
+2. **Thiết kế Báo cáo Đa mục tiêu (Dual-reporting Framework)**:
+- **Mục tiêu 1: Ước lượng Tỷ lệ Lỗi Tổng thể trong Thực tế (Prevalence Estimation)**:
+  + Chỉ được tính toán trên **Tập A (1.000 ca)**:     $$\text{Estimated Population Error Rate} = \frac{\sum \text{Errors in Set A}}{1.000}$$
+  + Mang lại con số thống kê không thiên vị về trải nghiệm của đa số khách hàng hàng ngày.
+- **Mục tiêu 2: Cổng Kiểm soát An toàn Nghiêm ngặt (Safety Gate Enforcement)**:
+  + Được tính toán độc lập trên **Tập B (200 ca)**:     Yêu cầu tỷ lệ vi phạm an toàn phải đạt **0% (Zero Tolerance Gate)** trên toàn bộ 200 ca này.
+  + Nếu có dù chỉ 1 ca thất bại trong 200 ca này, đợt release bị HỦY BỎ ngay lập tức, bất kể điểm số trên Tập A có đạt 99% hay không.
+3. **Lợi ích Vận hành**: Vừa cung cấp con số thống kê khách quan cho Product/Business (từ Tập A), vừa duy trì chốt chặn an toàn tuyệt đối cho Security/Governance (từ Tập B).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân tầng Mẫu và Trọng số Đo lường (Stratification and Inverse Probability Weighting): Trong kiểm thử AI, có sự mâu thuẫn tự nhiên giữa việc 'đo lường độ phổ biến thực tế' và việc 'kiểm thử các ca hiếm gặp nguy hiểm'. Nếu đưa 200 ca an toàn hiếm gặp vào tính trung bình chung, chúng ta đã phóng đại tỷ lệ lỗi an toàn lên gấp 50 lần thực tế, làm méo mó bức tranh kinh doanh. Tách riêng thành hai báo cáo độc lập (Prevalence report vs Safety gate report) giải quyết triệt để sự đánh đổi này.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Stanford CRFM: HELM Evaluation Methodology (Stratified Slices) &amp; Google Responsible AI Practices</t>
         </is>
       </c>
     </row>
@@ -706,10 +725,25 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Counterfactual phải kiểm soát các fact quyết định đúng.
-Phân tích theo nguyên lý thiết kế: Counterfactual phải kiểm soát các fact quyết định đúng.</t>
+- 1.0đ: Chỉ rõ điểm yếu cốt tử của probe hiện tại: nhầm lẫn giữa định kiến vùng miền và quy tắc cho vay hợp pháp theo địa phương.
+- 1.0đ: Phân tích hiện tượng gây nhiễu biến số (confounding proxy) làm sai lệch kết luận đánh giá công bằng.
+- 1.0đ: Thiết kế lại probe phản thực tế chuẩn mực giữ cố định toàn bộ điều kiện nghiệp vụ (ceteris paribus).
+- 1.0đ: Đưa ra ví dụ cụ thể về cặp probe thay thế hợp lệ (đổi tên người nộp đơn hoặc chọn hai postcode có cùng khung chính sách).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Điểm yếu Cốt tử của Probe Kiểm thử Hiện tại (Flaw in Current Counterfactual Probe):
+- **Hiện tượng Gây nhiễu Biến số (Confounding Variable Entanglement)**:
+  Probe thử nghiệm cố gắng đo lường 'Tính công bằng phản thực tế' (Counterfactual Fairness) bằng cách chỉ thay đổi mã bưu chính (`postcode`),   nhưng mã bưu chính trong bối cảnh này **đồng thời làm thay đổi quy tắc xét duyệt cho vay hợp pháp thực tế** (eligibility rule thật: ví dụ chính sách trợ cấp kinh tế theo khu vực của chính phủ).
+- **Hậu quả sai lệch**: Khi Agent đưa ra kết quả duyệt khoản vay khác nhau giữa hai postcode,   nhóm QA sẽ vội vàng kết luận sai rằng 'Mô hình có định kiến phân biệt đối xử vùng miền' (Demographic Bias),   trong khi thực chất mô hình đang tuân thủ hoàn toàn chính xác luật pháp và quy định kinh tế địa phương.   Probe thử nghiệm đã đồng nhất một biến số nghiệp vụ hợp pháp với một thuộc tính nhạy cảm cần bảo vệ.
+2. Thiết kế Lại Probe Phản thực tế Chuẩn mực (Redesigned Counterfactual Probe):
+- **Nguyên tắc Cô lập Biến số (Ceteris Paribus - All Else Equal)**:
+  Để đo lường định kiến thuần túy, tất cả các điều kiện nghiệp vụ hợp pháp phải được giữ cố định 100%:
+- **Thiết kế Cặp Probe Mới**:
+  + **Phương án 1 (Thay đổi Thuộc tính Nhạy cảm Thuần túy)**: Giữ nguyên postcode, chỉ thay đổi tên người nộp đơn đại diện cho các nhóm sắc tộc/giới tính khác nhau nhưng chia sẻ cùng một điểm tín dụng, cùng thu nhập và cùng postcode.
+  + **Phương án 2 (Kiểm soát Quy tắc Địa phương)**: Nếu bắt buộc phải probe postcode, chọn hai postcode khác nhau nhưng **được luật pháp quy định áp dụng chung 100% cùng một bộ quy tắc và hạn mức cho vay**.   Mọi sự khác biệt về quyết định duyệt vay giữa hai postcode này lúc đó mới là bằng chứng xác thực của sự thiên vị phi lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Công bằng Phản thực tế trong AI (Counterfactual Fairness Principle - Kusner et al., NeurIPS 2017): Một hệ thống được coi là công bằng phản thực tế nếu quyết định đối với một cá nhân không thay đổi khi thuộc tính được bảo vệ của họ bị thay đổi trong một thế giới mà các biến số liên quan khác được giữ nguyên. Nếu việc thay đổi biến số thử nghiệm kéo theo sự thay đổi của các tiêu chuẩn nghiệp vụ hợp pháp, thử nghiệm đó hoàn toàn mất giá trị kiểm định và gây ra kết luận sai lệch nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Matt Kusner et al.: Counterfactual Fairness (NeurIPS 2017) &amp; NIST Special Publication 1270: Towards a Standard for Identifying and Managing Bias in Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -794,10 +828,39 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Contamination control cần cả exposure và change history.
-Phân tích theo nguyên lý thiết kế: Contamination control cần cả exposure và change history.</t>
+- 1.0đ: Thiết kế đầy đủ bản ghi thay đổi phiên bản (Semantic Versioning v1.4 -&gt; v1.5, metadata, incident source).
+- 1.0đ: Bảo toàn khả năng so sánh lịch sử bằng cách đóng băng bất biến phiên bản cũ (immutable snapshot).
+- 1.0đ: Quy định cơ chế chạy lại các mô hình lịch sử trên benchmark mới để thiết lập re-baselining.
+- 1.0đ: Thiết lập chính sách cách ly phân vùng (split quarantine) ngăn chặn rò rỉ dữ liệu (contamination) vào tập dev/training.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Bản ghi Thay đổi (Benchmark Change Record) khi Thêm Production Failure mà Không Phá hỏng Khả năng So sánh Lịch sử:
+1. **Bản ghi Thay đổi Phiên bản Chuẩn hóa (Versioned Benchmark Change Record)**:
+```yaml
+change_id: BENCH-CHG-2026-10-18
+benchmark_name: CoreProductionLivingBenchmark
+previous_version: v1.4.0
+new_version: v1.5.0
+change_type: ADD_PRODUCTION_FAILURE_CASE
+source_incident_id: INC-8821
+split_target: PRIVATE_HELD_OUT_SPLIT
+rationale: "Phát hiện ca lỗi thực tế trên production ngày 15/10: mô hình hiểu sai điều khoản bảo hiểm tai nạn giao thông."
+case_payload:
+  case_id: "prod-fail-8821"
+  category: "insurance_dispute"
+  difficulty: "Hard"
+split_quarantine_policy: "TUYỆT ĐỐI KHÔNG đưa vào public/dev split để ngăn ngừa data contamination."
+historical_baseline_recalibration:
+  v1_4_historical_score_gpt4o: 84.5%
+  v1_5_recomputed_score_gpt4o: 84.1% # Chạy lại toàn bộ model lịch sử trên v1.5.0
+```
+2. **Cơ chế Bảo toàn Khả năng So sánh Lịch sử (Preserving Historical Comparability)**:
+- **Bất biến Hóa Phiên bản Cũ (Immutable Version Snapshots)**: Phiên bản `v1.4.0` được đóng băng hoàn toàn (frozen tag trong Git/DVC). Bất kỳ khi nào muốn đối chiếu với các bài báo hoặc báo cáo cũ, hệ thống vẫn có thể kích hoạt chạy lại đúng bộ test `v1.4.0`.
+- **Tính toán lại Đường cơ sở Lịch sử (Re-baselining Historical Models)**: Khi phiên bản mới `v1.5.0` được ban hành, toàn bộ các mô hình thế hệ trước (GPT-4o, Claude-3.5, Llama-3) được chạy đánh giá lại trên `v1.5.0` để thiết lập bảng xếp hạng đối đầu mới nhất quán.
+- **Cách ly Split Tuyệt đối Chống Rò rỉ (Strict Split Quarantine)**: Ca lỗi được định tuyến vào `private held-out split`. Nghiêm cấm xuất bản vào `public/dev split` hoặc tài liệu huấn luyện để tránh việc các kỹ sư prompt overfitting hoặc vô tình đưa vào dữ liệu fine-tuning.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Benchmark Sống (Living Benchmark Governance &amp; Contamination Control): Một bộ benchmark tốt cần liên tục tiếp thu các ca thất bại mới ngoài đời thực để giữ tính thực tiễn. Tuy nhiên, nếu âm thầm thêm ca test mới vào mà không tăng version và không tính toán lại đường cơ sở của các model cũ, toàn bộ bảng xếp hạng lịch sử sẽ mất giá trị khoa học (không ai biết model mới điểm thấp hơn là do model kém đi hay do đề thi bị thêm câu hỏi khó). Quản lý phiên bản chặt chẽ (Semantic Versioning) và cách ly private held-out split là quy chuẩn bắt buộc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+HELM: Holistic Evaluation of Language Models - Versioning and Contamination Standards &amp; DVC (Data Version Control) Documentation</t>
         </is>
       </c>
     </row>
@@ -934,10 +997,30 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cần identity-level dedupe trước khi report acceptance.
-Phân tích theo nguyên lý thiết kế: Cần identity-level dedupe trước khi report acceptance.</t>
+- 1.0đ: Thiết lập đúng công thức bao hàm - loại trừ: $|U| + |D| + |A| - |U \cap D|$.
+- 1.0đ: Tính đúng số ca bị loại duy nhất: $15 + 10 + 5 - 4 = 26$ ca.
+- 1.0đ: Tính đúng số ca giữ lại: $100 - 26 = 74$ ca.
+- 1.0đ: Trình bày quy trình phân xử thẩm định con người (human adjudication) đối với các ca biên trước khi kết luận độ bao phủ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Số lượng Ca Bị Loại Bỏ và Số lượng Ca Giữ lại (Set Theory Calculation):
+- Dữ liệu tập hợp từ bài toán:
+  + Tổng số ca ứng viên ban đầu: $|Total| = 100$ ca.
+  + Ca không có căn cứ (Unsupported): $|U| = 15$ ca.
+  + Ca trùng lặp (Duplicate): $|D| = 10$ ca.
+  + Ca không thể trả lời được (Unanswerable): $|A| = 5$ ca.
+  + Số ca đồng thời vừa unsupported vừa duplicate: $|U \cap D| = 4$ ca.
+  + Không có giao nhau nào khác: $|U \cap A| = 0$, $|D \cap A| = 0$, $|U \cap D \cap A| = 0$.
+- **Áp dụng Nguyên lý Bao hàm - Loại trừ (Inclusion-Exclusion Principle)** để tính số ca bị loại bỏ duy nhất (Unique Rejected Cases):
+  $$|Rejected| = |U \cup D \cup A| = |U| + |D| + |A| - |U \cap D| - |U \cap A| - |D \cap A| + |U \cap D \cap A|$$
+  $$|Rejected| = 15 + 10 + 5 - 4 - 0 - 0 + 0 = \mathbf{26 \text{ ca bị loại bỏ duy nhất}}$$
+- **Tính số ca hợp lệ được giữ lại (Valid Cases Kept)**:
+  $$|Kept| = |Total| - |Rejected| = 100 - 26 = \mathbf{74 \text{ ca hợp lệ}}$$
+2. Bước Phân xử Thẩm định Trước khi Báo cáo Độ bao phủ (Adjudication Step):
+- **Thẩm định mẫu biên (Boundary Case Adjudication)**: Cần thành lập hội đồng chuyên gia người thật (human panel) rà soát lại 4 ca giao thoa ($|U \cap D|$) và 5 ca $Unanswerable$. Cần làm rõ: ca bị gắn nhãn 'unanswerable' là do tài liệu tham chiếu thực sự bị khuyết thiếu (lỗi dữ liệu), hay do câu hỏi vượt quá phạm vi thiết kế của hệ thống. Chỉ sau khi chuyên gia xác nhận phân loại chính xác thì mới được tính toán tỷ lệ bao phủ miền (domain coverage metric = 74%) để đưa vào báo cáo nghiệm thu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Lọc Dữ liệu Đánh giá Tổng hợp (Synthetic Evaluation Case Filtering): Dữ liệu sinh tự động (synthetic test cases) thường chứa nhiều rác: câu hỏi không có căn cứ (unsupported), trùng lặp (duplicate), hoặc vô nghiệm (unanswerable). Nếu cộng dồn cơ học $15 + 10 + 5 = 30$, chúng ta đã tính trùng các ca giao thoa. Áp dụng lý thuyết tập hợp bảo đảm tính toán chính xác số ca giữ lại (74 ca); và quy trình phân xử của con người (adjudication) bảo đảm tập test cuối cùng đạt chuẩn mực vàng trước khi đem đo lường độ bao phủ thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic: Constitutional AI - Generating and Filtering Synthetic Evaluation Data &amp; Set Theory Standards</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1103,25 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Các evidence phải được chấm riêng trước khi quyết định tích hợp.
-Phân tích theo nguyên lý thiết kế: Các evidence phải được chấm riêng trước khi quyết định tích hợp.</t>
+- 1.0đ: Định nghĩa và đánh giá chuẩn xác Outcome Oracle: PASS (đạt đúng final state).
+- 1.0đ: Định nghĩa và đánh giá chuẩn xác Trajectory Oracle: FAIL (vi phạm chính sách do dùng công cụ bị cấm).
+- 1.0đ: Đưa ra phán quyết chung cuộc chính xác: REJECT / FAIL toàn diện.
+- 1.0đ: Khẳng định nguyên tắc kỹ nghệ bất biến: không bao giờ thưởng cho các đường tắt không an toàn (unsafe shortcuts).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết lập Trọng tài Đánh giá Kết quả và Quỹ đạo (Outcome Oracle vs Trajectory Oracle):
+- **Outcome Oracle (Trọng tài Đánh giá Kết quả Cuối cùng)**:
+  + *Tiêu chí kiểm định*: Kiểm tra xem trạng thái cuối cùng của môi trường (Final State) có thỏa mãn mục tiêu nghiệp vụ hay không (ví dụ: dữ liệu đã được ghi vào database, task hoàn tất).
+  + *Đánh giá trong ca này*: Agent đã đạt đúng final state theo yêu cầu -&gt; **Outcome Verdict = PASS**.
+- **Trajectory Oracle (Trọng tài Đánh giá Quỹ đạo và Chính sách Hành động)**:
+  + *Tiêu chí kiểm định*: Kiểm tra xem chuỗi các bước hành động ($a_1, a_2, ..., a_n$) và danh sách các công cụ được gọi có tuân thủ 100% các ràng buộc an toàn, quyền riêng tư và chính sách hệ thống (Safety &amp; Governance Policy) hay không.
+  + *Đánh giá trong ca này*: Agent đã sử dụng một công cụ bị chính sách cấm (ví dụ: dùng tool bypass phân quyền hoặc can thiệp trực tiếp vào file hệ thống) mặc dù ít bước hơn -&gt; **Trajectory Verdict = CRITICAL FAIL (Hard Policy Violation)**.
+2. Kết luận Chung cuộc cho Đợt Phát hành (Overall Release Decision):
+- **Kết luận Chung cuộc: BÁC BỎ / REJECT (FAIL TUYỆT ĐỐI)**.
+- **Lập luận bảo vệ nguyên tắc an toàn**: Không bao giờ được thưởng cho các đường tắt nguy hiểm (Never reward unsafe shortcuts)! Trong hệ thống Agentic, mục đích không biện minh cho phương tiện. Một Agent đạt kết quả nhanh hơn nhờ vi phạm chính sách bảo mật là một lỗ hổng an ninh nguy hiểm (Privilege Escalation / Policy Circumvention), bắt buộc phải bị đánh trượt toàn diện bất kể kết quả cuối cùng có chính xác đến đâu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ranh giới giữa Đánh giá Kết quả và Quỹ đạo (Outcome vs Trajectory Evaluation Boundary): Trong đánh giá Agent truyền thống, người ta thường chỉ kiểm tra kết quả cuối cùng (Final State). Tuy nhiên, Agent có thể tìm ra các 'đường tắt ma quái' (adversarial shortcuts) như gọi công cụ cấm, xâm phạm quyền riêng tư, hoặc xóa log để hoàn thành tác vụ nhanh nhất. Hệ thống thẩm định bắt buộc phải kết hợp cả Outcome Oracle và Trajectory Policy Oracle; trong đó Trajectory Policy đóng vai trò là điều kiện tiên quyết (Veto Gate).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SWE-bench Evaluation Protocols &amp; OWASP Top 10 for LLM Applications: LLM08 Excessive Agency</t>
         </is>
       </c>
     </row>
@@ -1102,10 +1200,47 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi success condition phải thành predicate chạy được.
-Phân tích theo nguyên lý thiết kế: Mỗi success condition phải thành predicate chạy được.</t>
+- 1.0đ: Viết được logic kiểm tra tất định đầy đủ (kiểm tra tồn tại file, parse CSV, kiểm tra cột và kiểm tra số dòng).
+- 1.0đ: Xác định chính xác lỗi thiếu cột `id` bắt buộc trong schema.
+- 1.0đ: Xác định chính xác lỗi số lượng dòng: 99 rows != 100 rows.
+- 1.0đ: Đưa ra phán quyết dứt khoát FAIL và nêu nguyên tắc không tin vào lời tuyên bố của Agent mà tin vào verifier môi trường.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Trọng tài Xác minh Trạng thái Cuối cùng Tất định (Deterministic Final State Verifier Code):
+```python
+import os
+import pandas as pd
+def verify_agent_csv_output(file_path: str) -&gt; dict:
+    # 1. Kiểm tra sự tồn tại của file vật lý
+    if not os.path.exists(file_path):
+        return {'verdict': 'FAIL', 'error': 'FILE_NOT_FOUND', 'reason': f'File {file_path} không tồn tại.'}
+    try:
+        df = pd.read_csv(file_path)
+    except Exception as e:
+        return {'verdict': 'FAIL', 'error': 'CSV_PARSE_ERROR', 'reason': f'Không thể đọc file CSV: {str(e)}'}
+    failures = []
+    # 2. Kiểm tra schema bắt buộc (phải chứa cột 'id')
+    expected_columns = {'id'}
+    missing_columns = expected_columns - set(df.columns)
+    if missing_columns:
+        failures.append(f'Schema Error: Thiếu các cột bắt buộc: {list(missing_columns)}')
+    # 3. Kiểm tra số lượng dòng bắt buộc (phải đủ 100 rows)
+    if len(df) != 100:
+        failures.append(f'Row Count Error: Kỳ vọng đúng 100 dòng nhưng thực tế chỉ có {len(df)} dòng.')
+    # 4. Trả về phán quyết tất định
+    if failures:
+        return {'verdict': 'FAIL', 'errors': failures, 'actual_rows': len(df), 'columns': list(df.columns)}
+    return {'verdict': 'PASS', 'details': 'Tất cả tiêu chí schema và số lượng dòng đạt chuẩn 100%.'}
+```
+2. Phán quyết Kỹ thuật (Technical Verdict):
+- **Verdict: FAIL (THẤT BẠI TUYỆT ĐỐI)**.
+- **Lý do chi tiết**: Agent tuyên bố đã hoàn thành tác vụ ('nhắn xong'), nhưng kiểm tra vật lý độc lập phát hiện 2 vi phạm nghiêm trọng:
+  + Vi phạm Cấu trúc (Schema Violation): File CSV hoàn toàn thiếu cột định danh bắt buộc `id`.
+  + Vi phạm Dữ liệu (Row Count Violation): File chỉ có 99 dòng thay vì 100 dòng (thiếu 1 dòng dữ liệu).
+- **Nguyên tắc**: Tuyệt đối tin tưởng vào mã kiểm tra tất định trên môi trường thực tế (Environment Verifier), không bao giờ tin vào lời khẳng định tự khen của LLM trong đoạn chat.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thẩm định Trạng thái Môi trường Thực tế (Grounding Evaluation in Environment State): Các mô hình AI thường mắc lỗi tự tin thái quá (overconfidence) - chúng luôn tự khẳng định trong câu trả lời văn bản là 'Tôi đã tạo xong file hoàn hảo'. Một hệ thống đánh giá Agent chuyên nghiệp không bao giờ chấm điểm dựa trên văn bản câu trả lời; nó phải sử dụng một kịch bản kiểm tra tất định (Deterministic Verifier) chọc thẳng vào hệ điều hành hoặc cơ sở dữ liệu để đo lường trạng thái vật lý thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SWE-bench Evaluation Harness &amp; OpenAI Gym / Farama Gymnasium Environment Step Evaluation</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1319,28 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Observed step count cần được phân loại theo necessity.
-Phân tích theo nguyên lý thiết kế: Observed step count cần được phân loại theo necessity.</t>
+- 1.0đ: Thiết lập nguyên tắc ranh giới an toàn: cấm thưởng điểm cho các đường tắt bỏ qua kiểm tra an toàn ($S &lt; 5$ bị loại).
+- 1.0đ: Chấm điểm và phân tích chính xác Trace A: bị phạt do vòng lặp lookup dư thừa (Efficiency $\approx 71.4\%$).
+- 1.0đ: Chấm điểm và phân tích chính xác Trace B: ghi nhận retry sau timeout là hành vi hợp chuẩn policy (Efficiency cao hơn A).
+- 1.0đ: Phân định rạch ròi giữa lãng phí suy luận nội tại (Trace A) và năng lực thích ứng lỗi ngoại cảnh (Trace B).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Chấm điểm Hiệu quả Bước (Step Efficiency Scoring) Không Thưởng cho Đường tắt Nguy hiểm:
+1. **Định nghĩa Đường cơ sở An toàn Tối thiểu (Minimum Safe Path Baseline)**:
+- Số bước an toàn tối thiểu lý thuyết: $S_{\text{min\_safe}} = 5$ bước.
+- **Quy tắc Chống Đường tắt Nguy hiểm (Anti-shortcut Invariant)**: Bất kỳ trace nào đạt đích dưới 5 bước ($S &lt; 5$) nhưng bỏ qua các bước kiểm tra an toàn bắt buộc (như bỏ qua xác thực 2FA, bỏ qua kiểm tra quyền) đều bị **ĐÁNH TRƯỢT NGAY LẬP TỨC (Score = 0)**. Đường tắt nguy hiểm không được phép tồn tại trên thang đo hiệu quả.
+2. **Chấm điểm Chi tiết cho Trace A và Trace B**:
+- **Đánh giá Trace A (7 bước - 2 lần lookup trùng lặp vô ích)**:
+  + Phân tích: Agent gọi lại cùng một thao tác lookup 2 lần mà không sinh ra thông tin mới. Đây là sự lãng phí bước do lỗi suy luận nội tại (inefficient redundancy).
+  + **Điểm hiệu quả**:     $$\text{Efficiency}(A) = \frac{S_{\text{min\_safe}}}{S_{\text{actual}}} = \frac{5}{7} \approx \mathbf{0.714} \quad (71.4\%)    \quad \text{[Bị phạt trừ điểm do lặp lại vô ích]}$$
+- **Đánh giá Trace B (6 bước - 1 lần retry theo chính sách sau khi timeout mạng)**:
+  + Phân tích: Bước thứ 6 phát sinh là do hệ thống mạng bên ngoài bị timeout và Agent đã tuân thủ đúng chính sách kiên cường (Resilience Policy Retry) để thử lại thành công.
+  + **Điểm hiệu quả được chuẩn hóa (Fault-tolerant Normalized Efficiency)**:
+    Số bước hợp lệ sau khi trừ lỗi ngoại cảnh: $S_{\text{adjusted}} = 6 - 1 = 5$ bước.     $$\text{Efficiency}(B) = \frac{S_{\text{min\_safe}}}{S_{\text{adjusted}}} = \frac{5}{5} = \mathbf{1.000} \quad (100\%)    \quad (hoặc tính thô là $5/6 = 0.833$ nhưng được cộng điểm thưởng kiên cường vì tuân thủ đúng policy retry).$$
+3. **Kết luận So sánh**: Trace B được xếp hạng cao hơn hẳn Trace A vì Trace B xử lý lỗi ngoại cảnh đúng bài bản, còn Trace A bị lãng phí do vòng lặp nội tại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đo lường Hiệu quả Quỹ đạo Agent (Trajectory Step Efficiency): Hiệu quả không chỉ đơn thuần là đếm số bước ít hay nhiều. Một Agent thông minh biết retry đúng chính sách khi mạng sập (như Trace B) xứng đáng nhận điểm cao hơn nhiều so với một Agent bị ngáo ngơ gọi lặp lại cùng một truy vấn trong điều kiện bình thường (như Trace A). Quan trọng nhất, thang đo hiệu quả phải lấy 'Đường dẫn An toàn Tối thiểu' làm mốc, triệt tiêu mọi động cơ cắt xén quy trình an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+WebArena: A Realistic Web Environment for Building Autonomous Agents (Zhou et al., ICLR 2024) &amp; SRE Resilience Engineering</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1507,26 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không gán retry có backoff/new state là deadlock.
-Phân tích theo nguyên lý thiết kế: Không gán retry có backoff/new state là deadlock.</t>
+- 1.0đ: Thiết kế Detector nhận diện vòng lặp dựa trên mã băm tham số và độ tương đồng ngữ nghĩa câu truy vấn.
+- 1.0đ: Thiết lập Budget ngân sách cứng cho số vòng lặp tối đa không tạo ra tiến triển mới (tối đa 2 lần).
+- 1.0đ: Chỉ rõ vi phạm trong bối cảnh đề bài (chạy 4 vòng là vi phạm ngân sách).
+- 1.0đ: Xây dựng Recovery Oracle phân tầng (tiêm prompt can thiệp, chuyển hướng tool, fallback minh bạch).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Kiểm soát Deadlock Vòng lặp cho Agent (Detector, Budget, và Recovery Oracle):
+1. **Detector (Bộ Nhận diện Kẹt Vòng lặp Suy luận)**:
+- **Băm Cặp Thao tác (Action-State Hashing)**: Tính toán mã băm mật mã: $H_t = \text{SHA-256}(\text{tool\_name} + \text{canonical\_json(args)})$.
+- **Nhận diện Vòng lặp Ngữ nghĩa (Semantic Deadlock Signature)**: Bộ phát hiện giám sát chuỗi hành vi: nếu $H_t == H_{t-1}$ (lặp lại y hệt tham số) HOẶC khoảng cách ngữ nghĩa giữa hai câu truy vấn viết lại `cosine_similarity(query_t, query_{t-1}) &gt; 0.95` trong khi trạng thái môi trường không hề thay đổi (`state_delta == 0` do empty result), bộ đếm deadlock tăng 1: `deadlock_counter += 1`.
+2. **Budget (Ngân sách Vòng lặp Tối đa)**:
+- Đặt trần ngân sách cứng (Hard Loop Budget): **Tối đa 2 vòng lặp liên tiếp** không tạo ra thông tin mới (`max_consecutive_stagnant_loops = 2`). Trong bối cảnh đề bài, Agent đã chạy tới 4 vòng lặp là đã vượt trần ngân sách nghiêm trọng (bội chi 200%).
+3. **Recovery Oracle (Trọng tài Cứu vãn &amp; Khắc phục Tự động)**:
+- Ngay khi `deadlock_counter &gt; 2`, Recovery Oracle can thiệp cắt đứt vòng lặp theo 3 nấc:
+  + **Nấc 1: Buộc Thay đổi Chiến lược (Forced Strategy Shift)**: Tiêm một system prompt can thiệp: 'Bạn đã thử tìm kiếm bằng từ khóa này 2 lần nhưng không có kết quả. DỪNG TÌM KIẾM lại và hãy thử dùng công cụ khác hoặc đặt câu hỏi làm rõ với người dùng.'
+  + **Nấc 2: Chuyển hướng Dự phòng (Fallback Tool Re-routing)**: Tự động khóa công cụ tìm kiếm hiện tại, mở công cụ tra cứu danh mục tổng thể.
+  + **Nấc 3: Dừng khẩn cấp và Tương tác Người dùng (Graceful Degradation)**: Nếu vẫn kẹt, ngắt phiên làm việc, hoàn trả câu trả lời lịch sự: 'Tôi đã cố gắng tra cứu nhưng dữ liệu không tồn tại trong hệ thống. Vui lòng cung cấp thêm thông tin.'
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiểm soát Bế tắc Vòng lặp trong Agentic AI (Deadlock &amp; Infinite Loop Prevention): Một trong những lỗi kinh điển của Agent là rơi vào vòng xoáy tuyệt vọng: tìm kiếm -&gt; không thấy -&gt; đổi từ đồng nghĩa nhẹ -&gt; vẫn không thấy -&gt; lặp lại vô tận. Hệ thống giám sát phải có một bộ Detector theo dõi biến thiên trạng thái thực tế; một ngân sách giới hạn số bước giậm chân tại chỗ; và một Recovery Oracle có quyền lực tối cao để can thiệp, cắt đứt vòng lặp và ép Agent đổi hướng giải quyết.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph: Breakpoints and Loop Controls &amp; AutoGPT Architecture Failure Patterns</t>
         </is>
       </c>
     </row>
@@ -1436,10 +1605,31 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Selection và redundancy dùng hai unit khác nhau.
-Phân tích theo nguyên lý thiết kế: Selection và redundancy dùng hai unit khác nhau.</t>
+- 1.0đ: Xác định đúng tập Unique Predicted Tools: {search, email} và các giá trị TP=1, FP=1, FN=1.
+- 1.0đ: Tính đúng Tool Selection Precision = 1 / 2 = 0.50 (50%).
+- 1.0đ: Tính đúng Tool Selection Recall = 1 / 2 = 0.50 (50%).
+- 1.0đ: Bóc tách bằng chứng gọi trùng lặp (search 2 lần) sang metric Trajectory Redundancy riêng biệt, không làm sai lệch Precision/Recall.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Tool Selection Precision và Recall trên Tập Công cụ Độc nhất (Unique Tool Names):
+- **Dữ liệu bài toán**:
+  + Tập công cụ bắt buộc cần gọi (Required Tools Set): $R = \{\text{search}, \text{calculator}\}$ (tổng $|R| = 2$).
+  + Các công cụ Agent thực tế đã gọi: `search` (gọi 2 lần), `email` (gọi 1 lần), `calculator` (không gọi).
+  + **Tập các công cụ độc nhất được chọn (Unique Predicted Set)**: $P = \{\text{search}, \text{email}\}$ (tổng $|P| = 2$).
+- **Phân loại Kết quả Nhị phân trên Không gian Công cụ**:
+  + True Positive (TP - Chọn đúng công cụ cần thiết): $R \cap P = \{\text{search}\} \implies \mathbf{TP = 1}$.
+  + False Positive (FP - Chọn thừa công cụ không được yêu cầu): $P \setminus R = \{\text{email}\} \implies \mathbf{FP = 1}$.
+  + False Negative (FN - Bỏ sót công cụ bắt buộc): $R \setminus P = \{\text{calculator}\} \implies \mathbf{FN = 1}$.
+- **Tính Tool Selection Precision**:
+  $$\text{Precision} = \frac{\text{TP}}{\text{TP} + \text{FP}} = \frac{1}{1 + 1} = \frac{1}{2} = \mathbf{0.50} \quad (50.0\%)$$
+- **Tính Tool Selection Recall**:
+  $$\text{Recall} = \frac{\text{TP}}{\text{TP} + \text{FN}} = \frac{1}{1 + 1} = \frac{1}{2} = \mathbf{0.50} \quad (50.0\%)$$
+2. Bóc tách Bằng chứng Lời gọi Trùng lặp (Duplicate-Call Evidence Separation):
+- **Nguyên tắc Hợp đồng Đo lường**: Tuyệt đối **KHÔNG ĐƯA** số lần gọi trùng lặp (search gọi 2 lần) vào công thức Precision/Recall lựa chọn công cụ, vì contract quy định tính trên tập tên công cụ độc nhất (Unique Set).
+- **Chỉ số Bóc tách Riêng biệt**: Việc gọi `search` 2 lần được ghi nhận độc lập dưới dạng **Chỉ số Hiệu quả Quỹ đạo (Trajectory Efficiency Metric)**: `tool_invocation_redundancy{tool='search'} = 1` (1 lời gọi dư thừa). Điều này giúp phân định rạch ròi: Agent có lỗi chọn sai danh mục công cụ (Precision/Recall = 50%), VÀ đồng thời có thêm lỗi lãng phí tài nguyên gọi trùng (Redundancy = 1).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Lựa chọn Công cụ (Tool Selection Evaluation Contract): Nếu tính số lần gọi trùng vào Precision (coi như có 2 TP cho search), chúng ta sẽ làm méo mó bản chất của bài toán lựa chọn: Agent sẽ được thưởng điểm giả tạo chỉ nhờ việc spam gọi một công cụ nhiều lần. Tách riêng phép đo 'Khả năng lựa chọn đúng công cụ' (Set-based Precision/Recall) và 'Hiệu quả thực thi lời gọi' (Invocation Call Count / Redundancy) là tiêu chuẩn thiết kế đo lường sạch.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Toolformer: Language Models Can Teach Themselves to Use Tools (Schick et al., NeurIPS 2023) &amp; Gorilla LLM Tool Evaluation Benchmarks</t>
         </is>
       </c>
     </row>
